--- a/Car_Wash_Advisory_Top_Acquisitions.xlsx
+++ b/Car_Wash_Advisory_Top_Acquisitions.xlsx
@@ -43,7 +43,7 @@
     <t>Deal Value</t>
   </si>
   <si>
-    <t>Whistle Express Car Wash Acquires All Take 5 Car Wash's locations from Driven Brands</t>
+    <t>Whistle Express Car Wash Acquires Take 5 Car Wash</t>
   </si>
   <si>
     <t>653ad5a6e882f528b3301834</t>
@@ -52,204 +52,207 @@
     <t>Whistle Express Car Wash</t>
   </si>
   <si>
+    <t>Take 5 Car Wash</t>
+  </si>
+  <si>
+    <t>North Carolina</t>
+  </si>
+  <si>
+    <t>NC</t>
+  </si>
+  <si>
+    <t>$385 million</t>
+  </si>
+  <si>
+    <t>Magnolia Wash Holdings Receives A Growth Capital Investment from Oaktree Capital</t>
+  </si>
+  <si>
+    <t>Oaktree Capital</t>
+  </si>
+  <si>
+    <t>Magnolia Wash Holdings</t>
+  </si>
+  <si>
+    <t>Undisclosed</t>
+  </si>
+  <si>
+    <t>Alimentation Couche-Tard to acquire True Blue Car Wash</t>
+  </si>
+  <si>
+    <t>Alimentation Couche-Tard</t>
+  </si>
+  <si>
+    <t>True Blue Car Wash</t>
+  </si>
+  <si>
+    <t>Arizona</t>
+  </si>
+  <si>
+    <t>AZ</t>
+  </si>
+  <si>
+    <t>$395 million</t>
+  </si>
+  <si>
+    <t>ClearWater Express Wash acquires BlueWave Express Car Wash</t>
+  </si>
+  <si>
+    <t>ClearWater Express Wash</t>
+  </si>
+  <si>
+    <t>BlueWave Express Car Wash</t>
+  </si>
+  <si>
+    <t>Texas</t>
+  </si>
+  <si>
+    <t>TX</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>IMO Car Wash Group Acquires Goo-Goo 3 Minute Express Car Wash</t>
+  </si>
+  <si>
+    <t>IMO Car Wash Group</t>
+  </si>
+  <si>
+    <t>Goo-Goo 3 Minute Express Car Wash</t>
+  </si>
+  <si>
+    <t>Georgia</t>
+  </si>
+  <si>
+    <t>GA</t>
+  </si>
+  <si>
+    <t>Tsunami Express Acquires 53 Whistle Express Car Wash Sites</t>
+  </si>
+  <si>
+    <t>Tsunami Express</t>
+  </si>
+  <si>
+    <t>Illinois</t>
+  </si>
+  <si>
+    <t>IL</t>
+  </si>
+  <si>
+    <t>Alimentation Couche-Tard Acquires WetGo Car Wash</t>
+  </si>
+  <si>
+    <t>WetGo Car Wash</t>
+  </si>
+  <si>
+    <t>Virginia</t>
+  </si>
+  <si>
+    <t>VA</t>
+  </si>
+  <si>
+    <t>Warburg Pincus acquires El Car Wash</t>
+  </si>
+  <si>
+    <t>Warburg Pincus</t>
+  </si>
+  <si>
+    <t>El Car Wash</t>
+  </si>
+  <si>
+    <t>Florida</t>
+  </si>
+  <si>
+    <t>FL</t>
+  </si>
+  <si>
+    <t>Mister Car Wash acquires Clean Streak</t>
+  </si>
+  <si>
+    <t>Mister Car Wash</t>
+  </si>
+  <si>
+    <t>Clean Streak Ventures</t>
+  </si>
+  <si>
+    <t>$390M</t>
+  </si>
+  <si>
+    <t>Freeman Spogli &amp; Co. acquires White Water Car Wash</t>
+  </si>
+  <si>
+    <t>Freeman Spogli</t>
+  </si>
+  <si>
+    <t>WhiteWater Express Car Wash</t>
+  </si>
+  <si>
+    <t>Zips Car Wash acquires Boomerang Car Wash</t>
+  </si>
+  <si>
+    <t>ZIPS Car Wash</t>
+  </si>
+  <si>
+    <t>Boomerang Car Wash</t>
+  </si>
+  <si>
+    <t>Arkansas</t>
+  </si>
+  <si>
+    <t>AR</t>
+  </si>
+  <si>
+    <t>Club Car Wash acquires Rapid Xpress Car Wash</t>
+  </si>
+  <si>
+    <t>Club Car Wash</t>
+  </si>
+  <si>
+    <t>Rapid Xpress Car Wash</t>
+  </si>
+  <si>
+    <t>Tidal Wave Auto Spa acquires W4 Express Wash</t>
+  </si>
+  <si>
+    <t>Tidal Wave Auto Spa</t>
+  </si>
+  <si>
+    <t>W4 Express Wash</t>
+  </si>
+  <si>
+    <t>Ammori Equity Partners Acquires Zax Auto Wash</t>
+  </si>
+  <si>
+    <t>Ammori Equity Partners</t>
+  </si>
+  <si>
+    <t>Zax Auto Wash</t>
+  </si>
+  <si>
+    <t>Michigan</t>
+  </si>
+  <si>
+    <t>MI</t>
+  </si>
+  <si>
+    <t>Mister Car Wash acquires Prime Shine</t>
+  </si>
+  <si>
+    <t>Prime Shine Car Wash</t>
+  </si>
+  <si>
+    <t>California</t>
+  </si>
+  <si>
+    <t>CA</t>
+  </si>
+  <si>
+    <t>Driven Brands acquires Frank’s Car Wash Express</t>
+  </si>
+  <si>
     <t>Driven Brands</t>
   </si>
   <si>
-    <t>North Carolina</t>
-  </si>
-  <si>
-    <t>NC</t>
-  </si>
-  <si>
-    <t>$385 million</t>
-  </si>
-  <si>
-    <t>Magnolia Wash Holdings Receives A Growth Capital Investment from Oaktree Capital</t>
-  </si>
-  <si>
-    <t>Oaktree Capital</t>
-  </si>
-  <si>
-    <t>Magnolia Wash Holdings</t>
-  </si>
-  <si>
-    <t>Undisclosed</t>
-  </si>
-  <si>
-    <t>Alimentation Couche-Tard to acquire True Blue Car Wash</t>
-  </si>
-  <si>
-    <t>Alimentation Couche-Tard</t>
-  </si>
-  <si>
-    <t>True Blue Car Wash</t>
-  </si>
-  <si>
-    <t>Arizona</t>
-  </si>
-  <si>
-    <t>AZ</t>
-  </si>
-  <si>
-    <t>$395 million</t>
-  </si>
-  <si>
-    <t>ClearWater Express Wash acquires BlueWave Express Car Wash</t>
-  </si>
-  <si>
-    <t>ClearWater Express Wash</t>
-  </si>
-  <si>
-    <t>BlueWave Express Car Wash</t>
-  </si>
-  <si>
-    <t>Texas</t>
-  </si>
-  <si>
-    <t>TX</t>
-  </si>
-  <si>
-    <t>N/A</t>
-  </si>
-  <si>
-    <t>IMO Car Wash Group Acquires Goo-Goo 3 Minute Express Car Wash</t>
-  </si>
-  <si>
-    <t>IMO Car Wash Group</t>
-  </si>
-  <si>
-    <t>Goo-Goo 3 Minute Express Car Wash</t>
-  </si>
-  <si>
-    <t>Georgia</t>
-  </si>
-  <si>
-    <t>GA</t>
-  </si>
-  <si>
-    <t>Tsunami Express Acquires 53 Whistle Express Car Wash Sites</t>
-  </si>
-  <si>
-    <t>Tsunami Express</t>
-  </si>
-  <si>
-    <t>Illinois</t>
-  </si>
-  <si>
-    <t>IL</t>
-  </si>
-  <si>
-    <t>Alimentation Couche-Tard Acquires WetGo Car Wash</t>
-  </si>
-  <si>
-    <t>WetGo Car Wash</t>
-  </si>
-  <si>
-    <t>Virginia</t>
-  </si>
-  <si>
-    <t>VA</t>
-  </si>
-  <si>
-    <t>Warburg Pincus acquires El Car Wash</t>
-  </si>
-  <si>
-    <t>Warburg Pincus</t>
-  </si>
-  <si>
-    <t>El Car Wash</t>
-  </si>
-  <si>
-    <t>Florida</t>
-  </si>
-  <si>
-    <t>FL</t>
-  </si>
-  <si>
-    <t>Mister Car Wash acquires Clean Streak</t>
-  </si>
-  <si>
-    <t>Mister Car Wash</t>
-  </si>
-  <si>
-    <t>Clean Streak Ventures</t>
-  </si>
-  <si>
-    <t>$390M</t>
-  </si>
-  <si>
-    <t>Freeman Spogli &amp; Co. acquires White Water Car Wash</t>
-  </si>
-  <si>
-    <t>Freeman Spogli</t>
-  </si>
-  <si>
-    <t>WhiteWater Express Car Wash</t>
-  </si>
-  <si>
-    <t>Zips Car Wash acquires Boomerang Car Wash</t>
-  </si>
-  <si>
-    <t>ZIPS Car Wash</t>
-  </si>
-  <si>
-    <t>Boomerang Car Wash</t>
-  </si>
-  <si>
-    <t>Arkansas</t>
-  </si>
-  <si>
-    <t>AR</t>
-  </si>
-  <si>
-    <t>Club Car Wash acquires Rapid Xpress Car Wash</t>
-  </si>
-  <si>
-    <t>Club Car Wash</t>
-  </si>
-  <si>
-    <t>Rapid Xpress Car Wash</t>
-  </si>
-  <si>
-    <t>Tidal Wave Auto Spa acquires W4 Express Wash</t>
-  </si>
-  <si>
-    <t>Tidal Wave Auto Spa</t>
-  </si>
-  <si>
-    <t>W4 Express Wash</t>
-  </si>
-  <si>
-    <t>Ammori Equity Partners Acquires Zax Auto Wash</t>
-  </si>
-  <si>
-    <t>Ammori Equity Partners</t>
-  </si>
-  <si>
-    <t>Zax Auto Wash</t>
-  </si>
-  <si>
-    <t>Michigan</t>
-  </si>
-  <si>
-    <t>MI</t>
-  </si>
-  <si>
-    <t>Mister Car Wash acquires Prime Shine</t>
-  </si>
-  <si>
-    <t>Prime Shine Car Wash</t>
-  </si>
-  <si>
-    <t>California</t>
-  </si>
-  <si>
-    <t>CA</t>
-  </si>
-  <si>
-    <t>Driven Brands acquires Frank’s Car Wash Express</t>
-  </si>
-  <si>
     <t>Frank's Car Wash</t>
   </si>
   <si>
@@ -2144,9 +2147,6 @@
   </si>
   <si>
     <t>Links Car Wash Acquires Planned Take 5 Car Wash Development Site</t>
-  </si>
-  <si>
-    <t>Take 5 Car Wash</t>
   </si>
   <si>
     <t>Links Car Wash Acquires Rocket Shine Car Wash Site</t>
@@ -3444,10 +3444,10 @@
         <v>11</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>13</v>
+        <v>79</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E17" s="2">
         <v>44392.0</v>
@@ -3456,10 +3456,10 @@
         <v>0</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I17" s="4">
         <v>18.0</v>
@@ -3472,16 +3472,16 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E18" s="5">
         <v>44530.0</v>
@@ -3490,10 +3490,10 @@
         <v>0</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I18" s="4">
         <v>17.0</v>
@@ -3506,16 +3506,16 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>13</v>
+        <v>79</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E19" s="2">
         <v>44501.0</v>
@@ -3524,32 +3524,32 @@
         <v>0</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I19" s="4">
         <v>16.0</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K19" s="1"/>
       <c r="L19" s="1"/>
     </row>
     <row r="20">
       <c r="A20" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E20" s="2">
         <v>45882.0</v>
@@ -3558,10 +3558,10 @@
         <v>0</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I20" s="4">
         <v>15.0</v>
@@ -3574,7 +3574,7 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>11</v>
@@ -3583,7 +3583,7 @@
         <v>12</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E21" s="2">
         <v>45474.0</v>
@@ -3608,16 +3608,16 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E22" s="5">
         <v>44483.0</v>
@@ -3626,10 +3626,10 @@
         <v>0</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I22" s="4">
         <v>14.0</v>
@@ -3642,16 +3642,16 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E23" s="5">
         <v>44530.0</v>
@@ -3660,10 +3660,10 @@
         <v>0</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I23" s="4">
         <v>14.0</v>
@@ -3676,16 +3676,16 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E24" s="2">
         <v>39853.0</v>
@@ -3710,16 +3710,16 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E25" s="2">
         <v>41883.0</v>
@@ -3744,13 +3744,13 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>20</v>
@@ -3762,10 +3762,10 @@
         <v>0</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="I26" s="4">
         <v>12.0</v>
@@ -3778,7 +3778,7 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>11</v>
@@ -3787,7 +3787,7 @@
         <v>57</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E27" s="5">
         <v>45985.0</v>
@@ -3796,10 +3796,10 @@
         <v>0</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I27" s="4">
         <v>12.0</v>
@@ -3812,16 +3812,16 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E28" s="2">
         <v>44740.0</v>
@@ -3846,16 +3846,16 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E29" s="2">
         <v>44782.0</v>
@@ -3880,7 +3880,7 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>11</v>
@@ -3889,7 +3889,7 @@
         <v>64</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E30" s="2">
         <v>44774.0</v>
@@ -3914,16 +3914,16 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E31" s="2">
         <v>44927.0</v>
@@ -3948,16 +3948,16 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E32" s="5">
         <v>44523.0</v>
@@ -3966,10 +3966,10 @@
         <v>0</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I32" s="4">
         <v>11.0</v>
@@ -3982,16 +3982,16 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E33" s="2">
         <v>44211.0</v>
@@ -4000,10 +4000,10 @@
         <v>0</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="I33" s="4">
         <v>11.0</v>
@@ -4016,7 +4016,7 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>11</v>
@@ -4025,7 +4025,7 @@
         <v>59</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E34" s="5">
         <v>44852.0</v>
@@ -4050,16 +4050,16 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E35" s="2">
         <v>45568.0</v>
@@ -4084,16 +4084,16 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E36" s="2">
         <v>44624.0</v>
@@ -4118,7 +4118,7 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>11</v>
@@ -4127,7 +4127,7 @@
         <v>19</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E37" s="5">
         <v>44193.0</v>
@@ -4152,7 +4152,7 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>11</v>
@@ -4161,7 +4161,7 @@
         <v>52</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E38" s="2">
         <v>42828.0</v>
@@ -4186,16 +4186,16 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E39" s="2">
         <v>45876.0</v>
@@ -4204,10 +4204,10 @@
         <v>0</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="I39" s="4">
         <v>10.0</v>
@@ -4220,7 +4220,7 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>11</v>
@@ -4229,7 +4229,7 @@
         <v>57</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E40" s="2">
         <v>44291.0</v>
@@ -4238,10 +4238,10 @@
         <v>0</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I40" s="4">
         <v>10.0</v>
@@ -4254,16 +4254,16 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E41" s="2">
         <v>43867.0</v>
@@ -4272,10 +4272,10 @@
         <v>0</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I41" s="4">
         <v>9.0</v>
@@ -4288,16 +4288,16 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E42" s="2">
         <v>44823.0</v>
@@ -4322,7 +4322,7 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>11</v>
@@ -4331,7 +4331,7 @@
         <v>64</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E43" s="2">
         <v>44811.0</v>
@@ -4340,10 +4340,10 @@
         <v>0</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I43" s="4">
         <v>8.0</v>
@@ -4356,16 +4356,16 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>13</v>
+        <v>79</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E44" s="2">
         <v>44035.0</v>
@@ -4390,13 +4390,13 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>13</v>
+        <v>79</v>
       </c>
       <c r="D45" s="1" t="s">
         <v>20</v>
@@ -4408,10 +4408,10 @@
         <v>0</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I45" s="4">
         <v>8.0</v>
@@ -4424,16 +4424,16 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E46" s="2">
         <v>44070.0</v>
@@ -4458,16 +4458,16 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E47" s="2">
         <v>44671.0</v>
@@ -4492,16 +4492,16 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E48" s="5">
         <v>44910.0</v>
@@ -4510,10 +4510,10 @@
         <v>0</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I48" s="4">
         <v>8.0</v>
@@ -4526,16 +4526,16 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E49" s="2">
         <v>44629.0</v>
@@ -4560,16 +4560,16 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E50" s="5">
         <v>45274.0</v>
@@ -4594,16 +4594,16 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E51" s="2">
         <v>43601.0</v>
@@ -4612,10 +4612,10 @@
         <v>0</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I51" s="4">
         <v>8.0</v>
@@ -4628,7 +4628,7 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>11</v>
@@ -4637,7 +4637,7 @@
         <v>52</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E52" s="2">
         <v>43552.0</v>
@@ -4662,16 +4662,16 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E53" s="5">
         <v>45615.0</v>
@@ -4680,10 +4680,10 @@
         <v>0</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="I53" s="4">
         <v>8.0</v>
@@ -4696,16 +4696,16 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E54" s="2">
         <v>44823.0</v>
@@ -4730,16 +4730,16 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E55" s="2">
         <v>44682.0</v>
@@ -4748,10 +4748,10 @@
         <v>0</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="I55" s="4">
         <v>8.0</v>
@@ -4764,7 +4764,7 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>11</v>
@@ -4773,7 +4773,7 @@
         <v>23</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E56" s="2">
         <v>44385.0</v>
@@ -4798,7 +4798,7 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>11</v>
@@ -4807,7 +4807,7 @@
         <v>59</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E57" s="5">
         <v>44511.0</v>
@@ -4816,10 +4816,10 @@
         <v>0</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I57" s="4">
         <v>8.0</v>
@@ -4832,7 +4832,7 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>11</v>
@@ -4841,7 +4841,7 @@
         <v>59</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E58" s="2">
         <v>43594.0</v>
@@ -4866,16 +4866,16 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E59" s="5">
         <v>45615.0</v>
@@ -4884,10 +4884,10 @@
         <v>0</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="I59" s="4">
         <v>7.0</v>
@@ -4900,16 +4900,16 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>13</v>
+        <v>79</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E60" s="2">
         <v>43839.0</v>
@@ -4934,16 +4934,16 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>13</v>
+        <v>79</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E61" s="5">
         <v>43787.0</v>
@@ -4968,16 +4968,16 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E62" s="2">
         <v>44419.0</v>
@@ -5002,16 +5002,16 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E63" s="2">
         <v>44720.0</v>
@@ -5020,10 +5020,10 @@
         <v>0</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I63" s="4">
         <v>7.0</v>
@@ -5036,16 +5036,16 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E64" s="2">
         <v>45033.0</v>
@@ -5070,16 +5070,16 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E65" s="2">
         <v>46034.0</v>
@@ -5104,16 +5104,16 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E66" s="5">
         <v>43391.0</v>
@@ -5122,10 +5122,10 @@
         <v>0</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I66" s="4">
         <v>7.0</v>
@@ -5138,7 +5138,7 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>11</v>
@@ -5147,7 +5147,7 @@
         <v>52</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E67" s="2">
         <v>44095.0</v>
@@ -5156,10 +5156,10 @@
         <v>0</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="I67" s="4">
         <v>7.0</v>
@@ -5172,7 +5172,7 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>11</v>
@@ -5181,7 +5181,7 @@
         <v>52</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E68" s="2">
         <v>43003.0</v>
@@ -5190,10 +5190,10 @@
         <v>0</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I68" s="4">
         <v>7.0</v>
@@ -5206,7 +5206,7 @@
     </row>
     <row r="69">
       <c r="A69" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>11</v>
@@ -5215,7 +5215,7 @@
         <v>52</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E69" s="2">
         <v>43741.0</v>
@@ -5240,16 +5240,16 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E70" s="2">
         <v>44562.0</v>
@@ -5258,10 +5258,10 @@
         <v>0</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="I70" s="4">
         <v>7.0</v>
@@ -5274,16 +5274,16 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E71" s="2">
         <v>44774.0</v>
@@ -5292,10 +5292,10 @@
         <v>0</v>
       </c>
       <c r="G71" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H71" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I71" s="4">
         <v>7.0</v>
@@ -5308,7 +5308,7 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>11</v>
@@ -5317,7 +5317,7 @@
         <v>57</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E72" s="2">
         <v>44798.0</v>
@@ -5326,10 +5326,10 @@
         <v>0</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H72" s="1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="I72" s="4">
         <v>7.0</v>
@@ -5342,7 +5342,7 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>11</v>
@@ -5351,7 +5351,7 @@
         <v>57</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E73" s="5">
         <v>44195.0</v>
@@ -5376,7 +5376,7 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>11</v>
@@ -5385,7 +5385,7 @@
         <v>59</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E74" s="2">
         <v>43252.0</v>
@@ -5394,10 +5394,10 @@
         <v>0</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H74" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I74" s="4">
         <v>7.0</v>
@@ -5410,7 +5410,7 @@
     </row>
     <row r="75">
       <c r="A75" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>11</v>
@@ -5419,7 +5419,7 @@
         <v>59</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E75" s="2">
         <v>43007.0</v>
@@ -5428,10 +5428,10 @@
         <v>0</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H75" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I75" s="4">
         <v>7.0</v>
@@ -5444,13 +5444,13 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>13</v>
+        <v>79</v>
       </c>
       <c r="D76" s="1" t="s">
         <v>20</v>
@@ -5462,10 +5462,10 @@
         <v>0</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I76" s="4">
         <v>6.0</v>
@@ -5478,7 +5478,7 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>11</v>
@@ -5512,16 +5512,16 @@
     </row>
     <row r="78">
       <c r="A78" s="1" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="E78" s="2">
         <v>44566.0</v>
@@ -5530,10 +5530,10 @@
         <v>0</v>
       </c>
       <c r="G78" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H78" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="I78" s="4">
         <v>6.0</v>
@@ -5546,16 +5546,16 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E79" s="2">
         <v>44265.0</v>
@@ -5564,10 +5564,10 @@
         <v>0</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H79" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I79" s="4">
         <v>6.0</v>
@@ -5580,7 +5580,7 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>11</v>
@@ -5589,7 +5589,7 @@
         <v>52</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E80" s="2">
         <v>42779.0</v>
@@ -5614,16 +5614,16 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E81" s="2">
         <v>45448.0</v>
@@ -5632,10 +5632,10 @@
         <v>0</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H81" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I81" s="4">
         <v>6.0</v>
@@ -5648,16 +5648,16 @@
     </row>
     <row r="82">
       <c r="A82" s="1" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E82" s="2">
         <v>44287.0</v>
@@ -5666,10 +5666,10 @@
         <v>0</v>
       </c>
       <c r="G82" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H82" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I82" s="4">
         <v>6.0</v>
@@ -5682,16 +5682,16 @@
     </row>
     <row r="83">
       <c r="A83" s="1" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E83" s="2">
         <v>42401.0</v>
@@ -5700,10 +5700,10 @@
         <v>0</v>
       </c>
       <c r="G83" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H83" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="I83" s="4">
         <v>6.0</v>
@@ -5716,16 +5716,16 @@
     </row>
     <row r="84">
       <c r="A84" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E84" s="5">
         <v>45981.0</v>
@@ -5734,10 +5734,10 @@
         <v>0</v>
       </c>
       <c r="G84" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H84" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I84" s="4">
         <v>6.0</v>
@@ -5750,7 +5750,7 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>11</v>
@@ -5759,7 +5759,7 @@
         <v>23</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E85" s="5">
         <v>43762.0</v>
@@ -5784,7 +5784,7 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>11</v>
@@ -5793,7 +5793,7 @@
         <v>59</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E86" s="2">
         <v>44830.0</v>
@@ -5818,16 +5818,16 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="E87" s="2">
         <v>45630.0</v>
@@ -5836,10 +5836,10 @@
         <v>0</v>
       </c>
       <c r="G87" s="1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H87" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="I87" s="4">
         <v>6.0</v>
@@ -5852,16 +5852,16 @@
     </row>
     <row r="88">
       <c r="A88" s="1" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>13</v>
+        <v>79</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E88" s="5">
         <v>44482.0</v>
@@ -5870,10 +5870,10 @@
         <v>0</v>
       </c>
       <c r="G88" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H88" s="1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="I88" s="4">
         <v>5.0</v>
@@ -5886,7 +5886,7 @@
     </row>
     <row r="89">
       <c r="A89" s="1" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>11</v>
@@ -5895,7 +5895,7 @@
         <v>48</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E89" s="2">
         <v>45811.0</v>
@@ -5920,16 +5920,16 @@
     </row>
     <row r="90">
       <c r="A90" s="1" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E90" s="2">
         <v>44322.0</v>
@@ -5954,16 +5954,16 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="E91" s="2">
         <v>44684.0</v>
@@ -5988,16 +5988,16 @@
     </row>
     <row r="92">
       <c r="A92" s="1" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="E92" s="2">
         <v>43636.0</v>
@@ -6006,10 +6006,10 @@
         <v>0</v>
       </c>
       <c r="G92" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H92" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I92" s="4">
         <v>5.0</v>
@@ -6022,16 +6022,16 @@
     </row>
     <row r="93">
       <c r="A93" s="1" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E93" s="2">
         <v>44580.0</v>
@@ -6040,10 +6040,10 @@
         <v>0</v>
       </c>
       <c r="G93" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H93" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I93" s="4">
         <v>5.0</v>
@@ -6056,16 +6056,16 @@
     </row>
     <row r="94">
       <c r="A94" s="1" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E94" s="2">
         <v>44712.0</v>
@@ -6090,16 +6090,16 @@
     </row>
     <row r="95">
       <c r="A95" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="E95" s="5">
         <v>45943.0</v>
@@ -6124,16 +6124,16 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E96" s="2">
         <v>46034.0</v>
@@ -6158,16 +6158,16 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="E97" s="2">
         <v>44566.0</v>
@@ -6192,16 +6192,16 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="E98" s="2">
         <v>44818.0</v>
@@ -6226,7 +6226,7 @@
     </row>
     <row r="99">
       <c r="A99" s="1" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>11</v>
@@ -6235,7 +6235,7 @@
         <v>19</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="E99" s="2">
         <v>44475.0</v>
@@ -6244,10 +6244,10 @@
         <v>0</v>
       </c>
       <c r="G99" s="1" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H99" s="1" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="I99" s="4">
         <v>5.0</v>
@@ -6260,16 +6260,16 @@
     </row>
     <row r="100">
       <c r="A100" s="1" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E100" s="2">
         <v>44477.0</v>
@@ -6294,7 +6294,7 @@
     </row>
     <row r="101">
       <c r="A101" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>11</v>
@@ -6303,7 +6303,7 @@
         <v>52</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="E101" s="2">
         <v>44539.0</v>
@@ -6328,7 +6328,7 @@
     </row>
     <row r="102">
       <c r="A102" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>11</v>
@@ -6362,7 +6362,7 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>11</v>
@@ -6371,7 +6371,7 @@
         <v>52</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="E103" s="2">
         <v>44377.0</v>
@@ -6396,13 +6396,13 @@
     </row>
     <row r="104">
       <c r="A104" s="1" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="D104" s="1" t="s">
         <v>59</v>
@@ -6430,16 +6430,16 @@
     </row>
     <row r="105">
       <c r="A105" s="1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B105" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="E105" s="2">
         <v>45747.0</v>
@@ -6448,10 +6448,10 @@
         <v>0</v>
       </c>
       <c r="G105" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H105" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I105" s="4">
         <v>5.0</v>
@@ -6464,16 +6464,16 @@
     </row>
     <row r="106">
       <c r="A106" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B106" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="E106" s="2">
         <v>44760.0</v>
@@ -6498,16 +6498,16 @@
     </row>
     <row r="107">
       <c r="A107" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B107" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="E107" s="2">
         <v>44805.0</v>
@@ -6516,10 +6516,10 @@
         <v>0</v>
       </c>
       <c r="G107" s="1" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H107" s="1" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="I107" s="4">
         <v>5.0</v>
@@ -6532,7 +6532,7 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B108" s="1" t="s">
         <v>11</v>
@@ -6541,7 +6541,7 @@
         <v>23</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E108" s="2">
         <v>44042.0</v>
@@ -6566,16 +6566,16 @@
     </row>
     <row r="109">
       <c r="A109" s="1" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B109" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="E109" s="2">
         <v>44562.0</v>
@@ -6600,7 +6600,7 @@
     </row>
     <row r="110">
       <c r="A110" s="1" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B110" s="1" t="s">
         <v>11</v>
@@ -6609,7 +6609,7 @@
         <v>12</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E110" s="2">
         <v>45397.0</v>
@@ -6618,10 +6618,10 @@
         <v>0</v>
       </c>
       <c r="G110" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H110" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I110" s="4">
         <v>5.0</v>
@@ -6634,7 +6634,7 @@
     </row>
     <row r="111">
       <c r="A111" s="1" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B111" s="1" t="s">
         <v>11</v>
@@ -6643,7 +6643,7 @@
         <v>57</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="E111" s="2">
         <v>44538.0</v>
@@ -6652,10 +6652,10 @@
         <v>0</v>
       </c>
       <c r="G111" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H111" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I111" s="4">
         <v>5.0</v>
@@ -6668,7 +6668,7 @@
     </row>
     <row r="112">
       <c r="A112" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B112" s="1" t="s">
         <v>11</v>
@@ -6677,7 +6677,7 @@
         <v>59</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="E112" s="2">
         <v>42831.0</v>
@@ -6702,7 +6702,7 @@
     </row>
     <row r="113">
       <c r="A113" s="1" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B113" s="1" t="s">
         <v>11</v>
@@ -6711,7 +6711,7 @@
         <v>59</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E113" s="5">
         <v>44545.0</v>
@@ -6720,10 +6720,10 @@
         <v>0</v>
       </c>
       <c r="G113" s="1" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="H113" s="1" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="I113" s="4">
         <v>5.0</v>
@@ -6736,7 +6736,7 @@
     </row>
     <row r="114">
       <c r="A114" s="1" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B114" s="1" t="s">
         <v>11</v>
@@ -6745,7 +6745,7 @@
         <v>59</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="E114" s="2">
         <v>42929.0</v>
@@ -6770,7 +6770,7 @@
     </row>
     <row r="115">
       <c r="A115" s="1" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B115" s="1" t="s">
         <v>11</v>
@@ -6779,7 +6779,7 @@
         <v>59</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E115" s="2">
         <v>42786.0</v>
@@ -6788,10 +6788,10 @@
         <v>0</v>
       </c>
       <c r="G115" s="1" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H115" s="1" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="I115" s="4">
         <v>5.0</v>
@@ -6804,7 +6804,7 @@
     </row>
     <row r="116">
       <c r="A116" s="1" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B116" s="1" t="s">
         <v>11</v>
@@ -6813,7 +6813,7 @@
         <v>59</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="E116" s="2">
         <v>44777.0</v>
@@ -6838,16 +6838,16 @@
     </row>
     <row r="117">
       <c r="A117" s="1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B117" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E117" s="2">
         <v>45009.0</v>
@@ -6872,16 +6872,16 @@
     </row>
     <row r="118">
       <c r="A118" s="1" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B118" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="E118" s="2">
         <v>44531.0</v>
@@ -6890,10 +6890,10 @@
         <v>0</v>
       </c>
       <c r="G118" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H118" s="1" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="I118" s="4">
         <v>4.0</v>
@@ -6906,7 +6906,7 @@
     </row>
     <row r="119">
       <c r="A119" s="1" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B119" s="1" t="s">
         <v>11</v>
@@ -6940,16 +6940,16 @@
     </row>
     <row r="120">
       <c r="A120" s="1" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B120" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>13</v>
+        <v>79</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="E120" s="2">
         <v>44362.0</v>
@@ -6974,16 +6974,16 @@
     </row>
     <row r="121">
       <c r="A121" s="1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B121" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>13</v>
+        <v>79</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="E121" s="2">
         <v>43839.0</v>
@@ -7008,16 +7008,16 @@
     </row>
     <row r="122">
       <c r="A122" s="1" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B122" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>13</v>
+        <v>79</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="E122" s="2">
         <v>44004.0</v>
@@ -7026,10 +7026,10 @@
         <v>0</v>
       </c>
       <c r="G122" s="1" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H122" s="1" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="I122" s="4">
         <v>4.0</v>
@@ -7042,16 +7042,16 @@
     </row>
     <row r="123">
       <c r="A123" s="1" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B123" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>13</v>
+        <v>79</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="E123" s="2">
         <v>44334.0</v>
@@ -7060,10 +7060,10 @@
         <v>0</v>
       </c>
       <c r="G123" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H123" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="I123" s="4">
         <v>4.0</v>
@@ -7076,16 +7076,16 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B124" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>13</v>
+        <v>79</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="E124" s="2">
         <v>43839.0</v>
@@ -7110,16 +7110,16 @@
     </row>
     <row r="125">
       <c r="A125" s="1" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B125" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>13</v>
+        <v>79</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="E125" s="2">
         <v>44651.0</v>
@@ -7128,10 +7128,10 @@
         <v>0</v>
       </c>
       <c r="G125" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H125" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I125" s="4">
         <v>4.0</v>
@@ -7144,16 +7144,16 @@
     </row>
     <row r="126">
       <c r="A126" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B126" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>13</v>
+        <v>79</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="E126" s="2">
         <v>44826.0</v>
@@ -7162,10 +7162,10 @@
         <v>0</v>
       </c>
       <c r="G126" s="1" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H126" s="1" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="I126" s="4">
         <v>4.0</v>
@@ -7178,16 +7178,16 @@
     </row>
     <row r="127">
       <c r="A127" s="1" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B127" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="E127" s="2">
         <v>44678.0</v>
@@ -7212,16 +7212,16 @@
     </row>
     <row r="128">
       <c r="A128" s="1" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B128" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="E128" s="2">
         <v>44803.0</v>
@@ -7230,10 +7230,10 @@
         <v>0</v>
       </c>
       <c r="G128" s="1" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H128" s="1" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="I128" s="4">
         <v>4.0</v>
@@ -7246,7 +7246,7 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B129" s="1" t="s">
         <v>11</v>
@@ -7255,7 +7255,7 @@
         <v>19</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E129" s="2">
         <v>44937.0</v>
@@ -7280,7 +7280,7 @@
     </row>
     <row r="130">
       <c r="A130" s="1" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B130" s="1" t="s">
         <v>11</v>
@@ -7289,7 +7289,7 @@
         <v>19</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="E130" s="2">
         <v>44812.0</v>
@@ -7314,7 +7314,7 @@
     </row>
     <row r="131">
       <c r="A131" s="1" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B131" s="1" t="s">
         <v>11</v>
@@ -7323,7 +7323,7 @@
         <v>19</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="E131" s="2">
         <v>44812.0</v>
@@ -7348,7 +7348,7 @@
     </row>
     <row r="132">
       <c r="A132" s="1" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B132" s="1" t="s">
         <v>11</v>
@@ -7357,7 +7357,7 @@
         <v>19</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="E132" s="2">
         <v>44812.0</v>
@@ -7382,7 +7382,7 @@
     </row>
     <row r="133">
       <c r="A133" s="1" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B133" s="1" t="s">
         <v>11</v>
@@ -7391,7 +7391,7 @@
         <v>19</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="E133" s="2">
         <v>44617.0</v>
@@ -7416,7 +7416,7 @@
     </row>
     <row r="134">
       <c r="A134" s="1" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B134" s="1" t="s">
         <v>11</v>
@@ -7425,7 +7425,7 @@
         <v>19</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="E134" s="2">
         <v>44812.0</v>
@@ -7434,10 +7434,10 @@
         <v>0</v>
       </c>
       <c r="G134" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H134" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I134" s="4">
         <v>4.0</v>
@@ -7450,16 +7450,16 @@
     </row>
     <row r="135">
       <c r="A135" s="1" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B135" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="E135" s="2">
         <v>44567.0</v>
@@ -7484,16 +7484,16 @@
     </row>
     <row r="136">
       <c r="A136" s="1" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B136" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="E136" s="5">
         <v>44546.0</v>
@@ -7502,10 +7502,10 @@
         <v>0</v>
       </c>
       <c r="G136" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H136" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I136" s="4">
         <v>4.0</v>
@@ -7518,16 +7518,16 @@
     </row>
     <row r="137">
       <c r="A137" s="1" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B137" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="E137" s="5">
         <v>43769.0</v>
@@ -7536,10 +7536,10 @@
         <v>0</v>
       </c>
       <c r="G137" s="1" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="H137" s="1" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="I137" s="4">
         <v>4.0</v>
@@ -7552,7 +7552,7 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B138" s="1" t="s">
         <v>11</v>
@@ -7561,7 +7561,7 @@
         <v>52</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E138" s="2">
         <v>42877.0</v>
@@ -7586,7 +7586,7 @@
     </row>
     <row r="139">
       <c r="A139" s="1" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B139" s="1" t="s">
         <v>11</v>
@@ -7595,7 +7595,7 @@
         <v>52</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="E139" s="2">
         <v>43272.0</v>
@@ -7604,10 +7604,10 @@
         <v>0</v>
       </c>
       <c r="G139" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H139" s="1" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="I139" s="4">
         <v>4.0</v>
@@ -7620,7 +7620,7 @@
     </row>
     <row r="140">
       <c r="A140" s="1" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B140" s="1" t="s">
         <v>11</v>
@@ -7629,7 +7629,7 @@
         <v>52</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="E140" s="2">
         <v>44690.0</v>
@@ -7654,16 +7654,16 @@
     </row>
     <row r="141">
       <c r="A141" s="1" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B141" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="E141" s="2">
         <v>44467.0</v>
@@ -7672,10 +7672,10 @@
         <v>0</v>
       </c>
       <c r="G141" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H141" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I141" s="4">
         <v>4.0</v>
@@ -7688,16 +7688,16 @@
     </row>
     <row r="142">
       <c r="A142" s="1" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B142" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C142" s="6" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="E142" s="2">
         <v>45135.0</v>
@@ -7706,10 +7706,10 @@
         <v>0</v>
       </c>
       <c r="G142" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H142" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I142" s="4">
         <v>4.0</v>
@@ -7722,13 +7722,13 @@
     </row>
     <row r="143">
       <c r="A143" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B143" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D143" s="1" t="s">
         <v>20</v>
@@ -7756,16 +7756,16 @@
     </row>
     <row r="144">
       <c r="A144" s="1" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B144" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="E144" s="2">
         <v>44789.0</v>
@@ -7774,10 +7774,10 @@
         <v>0</v>
       </c>
       <c r="G144" s="1" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="H144" s="1" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="I144" s="4">
         <v>4.0</v>
@@ -7790,16 +7790,16 @@
     </row>
     <row r="145">
       <c r="A145" s="1" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B145" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="E145" s="5">
         <v>44522.0</v>
@@ -7808,10 +7808,10 @@
         <v>0</v>
       </c>
       <c r="G145" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H145" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="I145" s="4">
         <v>4.0</v>
@@ -7824,16 +7824,16 @@
     </row>
     <row r="146">
       <c r="A146" s="1" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B146" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="E146" s="2">
         <v>45026.0</v>
@@ -7842,10 +7842,10 @@
         <v>0</v>
       </c>
       <c r="G146" s="1" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H146" s="1" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="I146" s="4">
         <v>4.0</v>
@@ -7858,16 +7858,16 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B147" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E147" s="5">
         <v>44552.0</v>
@@ -7892,16 +7892,16 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B148" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="E148" s="5">
         <v>44497.0</v>
@@ -7910,10 +7910,10 @@
         <v>0</v>
       </c>
       <c r="G148" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H148" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I148" s="4">
         <v>4.0</v>
@@ -7926,16 +7926,16 @@
     </row>
     <row r="149">
       <c r="A149" s="1" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B149" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="E149" s="2">
         <v>45455.0</v>
@@ -7944,10 +7944,10 @@
         <v>0</v>
       </c>
       <c r="G149" s="1" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H149" s="1" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="I149" s="4">
         <v>4.0</v>
@@ -7960,16 +7960,16 @@
     </row>
     <row r="150">
       <c r="A150" s="1" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B150" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="E150" s="2">
         <v>44823.0</v>
@@ -7978,10 +7978,10 @@
         <v>0</v>
       </c>
       <c r="G150" s="1" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H150" s="1" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="I150" s="4">
         <v>4.0</v>
@@ -7994,7 +7994,7 @@
     </row>
     <row r="151">
       <c r="A151" s="1" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B151" s="1" t="s">
         <v>11</v>
@@ -8003,7 +8003,7 @@
         <v>57</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="E151" s="5">
         <v>44552.0</v>
@@ -8028,7 +8028,7 @@
     </row>
     <row r="152">
       <c r="A152" s="1" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B152" s="1" t="s">
         <v>11</v>
@@ -8037,7 +8037,7 @@
         <v>57</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="E152" s="2">
         <v>44606.0</v>
@@ -8046,10 +8046,10 @@
         <v>0</v>
       </c>
       <c r="G152" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H152" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I152" s="4">
         <v>4.0</v>
@@ -8062,7 +8062,7 @@
     </row>
     <row r="153">
       <c r="A153" s="1" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B153" s="1" t="s">
         <v>11</v>
@@ -8071,7 +8071,7 @@
         <v>57</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="E153" s="2">
         <v>44781.0</v>
@@ -8096,7 +8096,7 @@
     </row>
     <row r="154">
       <c r="A154" s="1" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B154" s="1" t="s">
         <v>11</v>
@@ -8105,7 +8105,7 @@
         <v>59</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="E154" s="2">
         <v>44714.0</v>
@@ -8114,10 +8114,10 @@
         <v>0</v>
       </c>
       <c r="G154" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H154" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I154" s="4">
         <v>4.0</v>
@@ -8130,7 +8130,7 @@
     </row>
     <row r="155">
       <c r="A155" s="1" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B155" s="1" t="s">
         <v>11</v>
@@ -8139,7 +8139,7 @@
         <v>59</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E155" s="5">
         <v>43098.0</v>
@@ -8164,16 +8164,16 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B156" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C156" s="1" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="E156" s="2">
         <v>45030.0</v>
@@ -8198,16 +8198,16 @@
     </row>
     <row r="157">
       <c r="A157" s="1" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B157" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C157" s="1" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="E157" s="2">
         <v>45750.0</v>
@@ -8232,16 +8232,16 @@
     </row>
     <row r="158">
       <c r="A158" s="1" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B158" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C158" s="1" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="E158" s="2">
         <v>45183.0</v>
@@ -8250,10 +8250,10 @@
         <v>0</v>
       </c>
       <c r="G158" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H158" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I158" s="4">
         <v>3.0</v>
@@ -8266,7 +8266,7 @@
     </row>
     <row r="159">
       <c r="A159" s="1" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B159" s="1" t="s">
         <v>11</v>
@@ -8275,7 +8275,7 @@
         <v>20</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="E159" s="2">
         <v>44958.0</v>
@@ -8284,10 +8284,10 @@
         <v>0</v>
       </c>
       <c r="G159" s="1" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H159" s="1" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="I159" s="4">
         <v>3.0</v>
@@ -8300,7 +8300,7 @@
     </row>
     <row r="160">
       <c r="A160" s="1" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B160" s="1" t="s">
         <v>11</v>
@@ -8309,7 +8309,7 @@
         <v>64</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="E160" s="2">
         <v>45798.0</v>
@@ -8318,10 +8318,10 @@
         <v>0</v>
       </c>
       <c r="G160" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H160" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I160" s="4">
         <v>3.0</v>
@@ -8334,16 +8334,16 @@
     </row>
     <row r="161">
       <c r="A161" s="1" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B161" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C161" s="1" t="s">
-        <v>13</v>
+        <v>79</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="E161" s="2">
         <v>44704.0</v>
@@ -8368,7 +8368,7 @@
     </row>
     <row r="162">
       <c r="A162" s="1" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B162" s="1" t="s">
         <v>11</v>
@@ -8377,7 +8377,7 @@
         <v>48</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="E162" s="2">
         <v>45701.0</v>
@@ -8402,7 +8402,7 @@
     </row>
     <row r="163">
       <c r="A163" s="1" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B163" s="1" t="s">
         <v>11</v>
@@ -8411,7 +8411,7 @@
         <v>48</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="E163" s="2">
         <v>44952.0</v>
@@ -8436,16 +8436,16 @@
     </row>
     <row r="164">
       <c r="A164" s="1" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B164" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C164" s="1" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E164" s="2">
         <v>45348.0</v>
@@ -8470,13 +8470,13 @@
     </row>
     <row r="165">
       <c r="A165" s="1" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B165" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C165" s="1" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="D165" s="1" t="s">
         <v>59</v>
@@ -8488,10 +8488,10 @@
         <v>0</v>
       </c>
       <c r="G165" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H165" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I165" s="4">
         <v>3.0</v>
@@ -8504,16 +8504,16 @@
     </row>
     <row r="166">
       <c r="A166" s="1" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B166" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C166" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="E166" s="2">
         <v>44299.0</v>
@@ -8538,16 +8538,16 @@
     </row>
     <row r="167">
       <c r="A167" s="1" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B167" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C167" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="E167" s="2">
         <v>44813.0</v>
@@ -8556,10 +8556,10 @@
         <v>0</v>
       </c>
       <c r="G167" s="1" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H167" s="1" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="I167" s="4">
         <v>3.0</v>
@@ -8572,16 +8572,16 @@
     </row>
     <row r="168">
       <c r="A168" s="1" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B168" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C168" s="1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="E168" s="2">
         <v>45050.0</v>
@@ -8590,10 +8590,10 @@
         <v>0</v>
       </c>
       <c r="G168" s="1" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H168" s="1" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="I168" s="4">
         <v>3.0</v>
@@ -8606,16 +8606,16 @@
     </row>
     <row r="169">
       <c r="A169" s="1" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B169" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C169" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="E169" s="5">
         <v>45943.0</v>
@@ -8640,16 +8640,16 @@
     </row>
     <row r="170">
       <c r="A170" s="1" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B170" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C170" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="E170" s="2">
         <v>45635.0</v>
@@ -8674,7 +8674,7 @@
     </row>
     <row r="171">
       <c r="A171" s="1" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B171" s="1" t="s">
         <v>11</v>
@@ -8683,7 +8683,7 @@
         <v>19</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="E171" s="2">
         <v>44707.0</v>
@@ -8708,16 +8708,16 @@
     </row>
     <row r="172">
       <c r="A172" s="1" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B172" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C172" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="E172" s="2">
         <v>44683.0</v>
@@ -8742,16 +8742,16 @@
     </row>
     <row r="173">
       <c r="A173" s="1" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B173" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C173" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="E173" s="2">
         <v>44750.0</v>
@@ -8760,10 +8760,10 @@
         <v>0</v>
       </c>
       <c r="G173" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H173" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I173" s="4">
         <v>3.0</v>
@@ -8776,16 +8776,16 @@
     </row>
     <row r="174">
       <c r="A174" s="1" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B174" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C174" s="1" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="E174" s="2">
         <v>44320.0</v>
@@ -8794,10 +8794,10 @@
         <v>0</v>
       </c>
       <c r="G174" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H174" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="I174" s="4">
         <v>3.0</v>
@@ -8810,16 +8810,16 @@
     </row>
     <row r="175">
       <c r="A175" s="1" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B175" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C175" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E175" s="2">
         <v>43405.0</v>
@@ -8837,14 +8837,14 @@
         <v>3.0</v>
       </c>
       <c r="J175" s="1" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="K175" s="1"/>
       <c r="L175" s="1"/>
     </row>
     <row r="176">
       <c r="A176" s="1" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B176" s="1" t="s">
         <v>11</v>
@@ -8853,7 +8853,7 @@
         <v>52</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="E176" s="5">
         <v>44525.0</v>
@@ -8878,7 +8878,7 @@
     </row>
     <row r="177">
       <c r="A177" s="1" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B177" s="1" t="s">
         <v>11</v>
@@ -8912,7 +8912,7 @@
     </row>
     <row r="178">
       <c r="A178" s="1" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B178" s="1" t="s">
         <v>11</v>
@@ -8921,7 +8921,7 @@
         <v>52</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="E178" s="2">
         <v>44776.0</v>
@@ -8930,10 +8930,10 @@
         <v>0</v>
       </c>
       <c r="G178" s="1" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="H178" s="1" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="I178" s="4">
         <v>3.0</v>
@@ -8946,16 +8946,16 @@
     </row>
     <row r="179">
       <c r="A179" s="1" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B179" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C179" s="1" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="E179" s="2">
         <v>44795.0</v>
@@ -8980,16 +8980,16 @@
     </row>
     <row r="180">
       <c r="A180" s="1" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B180" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C180" s="1" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="E180" s="2">
         <v>44424.0</v>
@@ -8998,10 +8998,10 @@
         <v>0</v>
       </c>
       <c r="G180" s="1" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H180" s="1" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="I180" s="4">
         <v>3.0</v>
@@ -9014,16 +9014,16 @@
     </row>
     <row r="181">
       <c r="A181" s="1" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B181" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C181" s="1" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="E181" s="2">
         <v>44978.0</v>
@@ -9048,16 +9048,16 @@
     </row>
     <row r="182">
       <c r="A182" s="1" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B182" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C182" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="E182" s="2">
         <v>44704.0</v>
@@ -9066,10 +9066,10 @@
         <v>0</v>
       </c>
       <c r="G182" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H182" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I182" s="4">
         <v>3.0</v>
@@ -9082,16 +9082,16 @@
     </row>
     <row r="183">
       <c r="A183" s="1" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B183" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C183" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="E183" s="2">
         <v>44454.0</v>
@@ -9100,10 +9100,10 @@
         <v>0</v>
       </c>
       <c r="G183" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H183" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I183" s="4">
         <v>3.0</v>
@@ -9116,16 +9116,16 @@
     </row>
     <row r="184">
       <c r="A184" s="1" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B184" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C184" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="E184" s="5">
         <v>44847.0</v>
@@ -9134,10 +9134,10 @@
         <v>0</v>
       </c>
       <c r="G184" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H184" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="I184" s="4">
         <v>3.0</v>
@@ -9150,16 +9150,16 @@
     </row>
     <row r="185">
       <c r="A185" s="1" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B185" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C185" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="E185" s="2">
         <v>45733.0</v>
@@ -9168,10 +9168,10 @@
         <v>0</v>
       </c>
       <c r="G185" s="1" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H185" s="1" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="I185" s="4">
         <v>3.0</v>
@@ -9184,7 +9184,7 @@
     </row>
     <row r="186">
       <c r="A186" s="1" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B186" s="1" t="s">
         <v>11</v>
@@ -9193,7 +9193,7 @@
         <v>23</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E186" s="2">
         <v>44379.0</v>
@@ -9218,7 +9218,7 @@
     </row>
     <row r="187">
       <c r="A187" s="1" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B187" s="1" t="s">
         <v>11</v>
@@ -9227,7 +9227,7 @@
         <v>39</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="E187" s="2">
         <v>45014.0</v>
@@ -9236,23 +9236,23 @@
         <v>0</v>
       </c>
       <c r="G187" s="1" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H187" s="1" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="I187" s="4">
         <v>3.0</v>
       </c>
       <c r="J187" s="1" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="K187" s="1"/>
       <c r="L187" s="1"/>
     </row>
     <row r="188">
       <c r="A188" s="1" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B188" s="1" t="s">
         <v>11</v>
@@ -9261,7 +9261,7 @@
         <v>20</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="E188" s="2">
         <v>44305.0</v>
@@ -9286,7 +9286,7 @@
     </row>
     <row r="189">
       <c r="A189" s="1" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B189" s="1" t="s">
         <v>11</v>
@@ -9295,7 +9295,7 @@
         <v>20</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="E189" s="2">
         <v>45877.0</v>
@@ -9304,10 +9304,10 @@
         <v>1</v>
       </c>
       <c r="G189" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H189" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I189" s="4">
         <v>3.0</v>
@@ -9320,7 +9320,7 @@
     </row>
     <row r="190">
       <c r="A190" s="1" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B190" s="1" t="s">
         <v>11</v>
@@ -9329,7 +9329,7 @@
         <v>12</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="E190" s="2">
         <v>45328.0</v>
@@ -9338,10 +9338,10 @@
         <v>0</v>
       </c>
       <c r="G190" s="1" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H190" s="1" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="I190" s="4">
         <v>3.0</v>
@@ -9354,7 +9354,7 @@
     </row>
     <row r="191">
       <c r="A191" s="1" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B191" s="1" t="s">
         <v>11</v>
@@ -9363,7 +9363,7 @@
         <v>12</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="E191" s="2">
         <v>45301.0</v>
@@ -9372,10 +9372,10 @@
         <v>0</v>
       </c>
       <c r="G191" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H191" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I191" s="4">
         <v>3.0</v>
@@ -9388,7 +9388,7 @@
     </row>
     <row r="192">
       <c r="A192" s="1" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B192" s="1" t="s">
         <v>11</v>
@@ -9397,7 +9397,7 @@
         <v>57</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="E192" s="2">
         <v>43853.0</v>
@@ -9422,7 +9422,7 @@
     </row>
     <row r="193">
       <c r="A193" s="1" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B193" s="1" t="s">
         <v>11</v>
@@ -9431,7 +9431,7 @@
         <v>57</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="E193" s="5">
         <v>44887.0</v>
@@ -9440,10 +9440,10 @@
         <v>0</v>
       </c>
       <c r="G193" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H193" s="1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="I193" s="4">
         <v>3.0</v>
@@ -9456,16 +9456,16 @@
     </row>
     <row r="194">
       <c r="A194" s="1" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B194" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C194" s="1" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="E194" s="2">
         <v>44700.0</v>
@@ -9490,7 +9490,7 @@
     </row>
     <row r="195">
       <c r="A195" s="1" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B195" s="1" t="s">
         <v>11</v>
@@ -9499,7 +9499,7 @@
         <v>59</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="E195" s="5">
         <v>44855.0</v>
@@ -9524,7 +9524,7 @@
     </row>
     <row r="196">
       <c r="A196" s="1" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B196" s="1" t="s">
         <v>11</v>
@@ -9533,7 +9533,7 @@
         <v>48</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="E196" s="2">
         <v>46107.0</v>
@@ -9558,7 +9558,7 @@
     </row>
     <row r="197">
       <c r="A197" s="1" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B197" s="1" t="s">
         <v>11</v>
@@ -9567,7 +9567,7 @@
         <v>20</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="E197" s="2">
         <v>45231.0</v>
@@ -9592,16 +9592,16 @@
     </row>
     <row r="198">
       <c r="A198" s="1" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B198" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C198" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="E198" s="2">
         <v>44810.0</v>
@@ -9626,16 +9626,16 @@
     </row>
     <row r="199">
       <c r="A199" s="1" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B199" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C199" s="1" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="E199" s="5">
         <v>44547.0</v>
@@ -9644,10 +9644,10 @@
         <v>0</v>
       </c>
       <c r="G199" s="1" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H199" s="1" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="I199" s="4">
         <v>2.0</v>
@@ -9660,13 +9660,13 @@
     </row>
     <row r="200">
       <c r="A200" s="1" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B200" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C200" s="1" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="D200" s="1" t="s">
         <v>59</v>
@@ -9678,10 +9678,10 @@
         <v>1</v>
       </c>
       <c r="G200" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H200" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I200" s="4">
         <v>2.0</v>
@@ -9694,16 +9694,16 @@
     </row>
     <row r="201">
       <c r="A201" s="1" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B201" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C201" s="1" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="E201" s="2">
         <v>43859.0</v>
@@ -9712,10 +9712,10 @@
         <v>0</v>
       </c>
       <c r="G201" s="1" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H201" s="1" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="I201" s="4">
         <v>2.0</v>
@@ -9728,7 +9728,7 @@
     </row>
     <row r="202">
       <c r="A202" s="1" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B202" s="1" t="s">
         <v>11</v>
@@ -9737,7 +9737,7 @@
         <v>64</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="E202" s="2">
         <v>45910.0</v>
@@ -9746,10 +9746,10 @@
         <v>0</v>
       </c>
       <c r="G202" s="1" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H202" s="1" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="I202" s="4">
         <v>2.0</v>
@@ -9762,16 +9762,16 @@
     </row>
     <row r="203">
       <c r="A203" s="1" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B203" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C203" s="1" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="E203" s="2">
         <v>45839.0</v>
@@ -9796,7 +9796,7 @@
     </row>
     <row r="204">
       <c r="A204" s="1" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B204" s="1" t="s">
         <v>11</v>
@@ -9805,7 +9805,7 @@
         <v>48</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="E204" s="2">
         <v>45559.0</v>
@@ -9830,7 +9830,7 @@
     </row>
     <row r="205">
       <c r="A205" s="1" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B205" s="1" t="s">
         <v>11</v>
@@ -9839,7 +9839,7 @@
         <v>48</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="E205" s="2">
         <v>45021.0</v>
@@ -9864,7 +9864,7 @@
     </row>
     <row r="206">
       <c r="A206" s="1" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B206" s="1" t="s">
         <v>11</v>
@@ -9873,7 +9873,7 @@
         <v>48</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="E206" s="2">
         <v>45066.0</v>
@@ -9898,7 +9898,7 @@
     </row>
     <row r="207">
       <c r="A207" s="1" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B207" s="1" t="s">
         <v>11</v>
@@ -9907,7 +9907,7 @@
         <v>48</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="E207" s="5">
         <v>45247.0</v>
@@ -9932,7 +9932,7 @@
     </row>
     <row r="208">
       <c r="A208" s="1" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B208" s="1" t="s">
         <v>11</v>
@@ -9941,7 +9941,7 @@
         <v>48</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="E208" s="5">
         <v>44529.0</v>
@@ -9966,16 +9966,16 @@
     </row>
     <row r="209">
       <c r="A209" s="1" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B209" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C209" s="1" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="E209" s="2">
         <v>45352.0</v>
@@ -10000,16 +10000,16 @@
     </row>
     <row r="210">
       <c r="A210" s="1" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B210" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C210" s="1" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="E210" s="2">
         <v>45993.0</v>
@@ -10034,16 +10034,16 @@
     </row>
     <row r="211">
       <c r="A211" s="1" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B211" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C211" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="E211" s="2">
         <v>44778.0</v>
@@ -10068,7 +10068,7 @@
     </row>
     <row r="212">
       <c r="A212" s="1" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B212" s="1" t="s">
         <v>11</v>
@@ -10077,7 +10077,7 @@
         <v>19</v>
       </c>
       <c r="D212" s="1" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="E212" s="2">
         <v>44728.0</v>
@@ -10086,10 +10086,10 @@
         <v>0</v>
       </c>
       <c r="G212" s="1" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H212" s="1" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="I212" s="4">
         <v>2.0</v>
@@ -10102,16 +10102,16 @@
     </row>
     <row r="213">
       <c r="A213" s="1" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B213" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C213" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D213" s="1" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="E213" s="5">
         <v>45281.0</v>
@@ -10136,16 +10136,16 @@
     </row>
     <row r="214">
       <c r="A214" s="1" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B214" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C214" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="E214" s="2">
         <v>44693.0</v>
@@ -10154,10 +10154,10 @@
         <v>0</v>
       </c>
       <c r="G214" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H214" s="1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="I214" s="4">
         <v>2.0</v>
@@ -10170,7 +10170,7 @@
     </row>
     <row r="215">
       <c r="A215" s="1" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B215" s="1" t="s">
         <v>11</v>
@@ -10179,7 +10179,7 @@
         <v>52</v>
       </c>
       <c r="D215" s="1" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="E215" s="2">
         <v>43636.0</v>
@@ -10188,10 +10188,10 @@
         <v>0</v>
       </c>
       <c r="G215" s="1" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H215" s="1" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="I215" s="4">
         <v>2.0</v>
@@ -10204,16 +10204,16 @@
     </row>
     <row r="216">
       <c r="A216" s="1" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B216" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C216" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D216" s="1" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="E216" s="2">
         <v>45530.0</v>
@@ -10238,16 +10238,16 @@
     </row>
     <row r="217">
       <c r="A217" s="1" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B217" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C217" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D217" s="1" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="E217" s="5">
         <v>44123.0</v>
@@ -10256,10 +10256,10 @@
         <v>0</v>
       </c>
       <c r="G217" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H217" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="I217" s="4">
         <v>2.0</v>
@@ -10272,16 +10272,16 @@
     </row>
     <row r="218">
       <c r="A218" s="1" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B218" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C218" s="1" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="D218" s="1" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="E218" s="2">
         <v>44798.0</v>
@@ -10290,10 +10290,10 @@
         <v>0</v>
       </c>
       <c r="G218" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H218" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I218" s="4">
         <v>2.0</v>
@@ -10306,16 +10306,16 @@
     </row>
     <row r="219">
       <c r="A219" s="1" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B219" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C219" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D219" s="1" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E219" s="5">
         <v>44552.0</v>
@@ -10340,16 +10340,16 @@
     </row>
     <row r="220">
       <c r="A220" s="1" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B220" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C220" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D220" s="1" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="E220" s="2">
         <v>45881.0</v>
@@ -10358,10 +10358,10 @@
         <v>0</v>
       </c>
       <c r="G220" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H220" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I220" s="4">
         <v>2.0</v>
@@ -10374,16 +10374,16 @@
     </row>
     <row r="221">
       <c r="A221" s="1" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B221" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C221" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D221" s="1" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E221" s="2">
         <v>44802.0</v>
@@ -10392,10 +10392,10 @@
         <v>0</v>
       </c>
       <c r="G221" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H221" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I221" s="4">
         <v>2.0</v>
@@ -10408,16 +10408,16 @@
     </row>
     <row r="222">
       <c r="A222" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B222" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C222" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D222" s="1" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="E222" s="2">
         <v>44231.0</v>
@@ -10426,10 +10426,10 @@
         <v>0</v>
       </c>
       <c r="G222" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H222" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I222" s="4">
         <v>2.0</v>
@@ -10442,16 +10442,16 @@
     </row>
     <row r="223">
       <c r="A223" s="1" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B223" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C223" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D223" s="1" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="E223" s="2">
         <v>43559.0</v>
@@ -10460,10 +10460,10 @@
         <v>0</v>
       </c>
       <c r="G223" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H223" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I223" s="4">
         <v>2.0</v>
@@ -10476,16 +10476,16 @@
     </row>
     <row r="224">
       <c r="A224" s="1" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B224" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C224" s="1" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="D224" s="1" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="E224" s="2">
         <v>44821.0</v>
@@ -10494,10 +10494,10 @@
         <v>0</v>
       </c>
       <c r="G224" s="1" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H224" s="1" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="I224" s="4">
         <v>2.0</v>
@@ -10510,16 +10510,16 @@
     </row>
     <row r="225">
       <c r="A225" s="1" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B225" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C225" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D225" s="1" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="E225" s="2">
         <v>44650.0</v>
@@ -10528,10 +10528,10 @@
         <v>0</v>
       </c>
       <c r="G225" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H225" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I225" s="4">
         <v>2.0</v>
@@ -10544,16 +10544,16 @@
     </row>
     <row r="226">
       <c r="A226" s="1" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B226" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C226" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D226" s="1" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="E226" s="2">
         <v>44701.0</v>
@@ -10562,10 +10562,10 @@
         <v>0</v>
       </c>
       <c r="G226" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H226" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I226" s="4">
         <v>2.0</v>
@@ -10578,16 +10578,16 @@
     </row>
     <row r="227">
       <c r="A227" s="1" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B227" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C227" s="1" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="D227" s="1" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="E227" s="5">
         <v>44847.0</v>
@@ -10596,10 +10596,10 @@
         <v>0</v>
       </c>
       <c r="G227" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H227" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I227" s="4">
         <v>2.0</v>
@@ -10612,16 +10612,16 @@
     </row>
     <row r="228">
       <c r="A228" s="1" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="B228" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C228" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D228" s="1" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="E228" s="2">
         <v>44727.0</v>
@@ -10630,10 +10630,10 @@
         <v>0</v>
       </c>
       <c r="G228" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H228" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I228" s="4">
         <v>2.0</v>
@@ -10646,16 +10646,16 @@
     </row>
     <row r="229">
       <c r="A229" s="1" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="B229" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C229" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D229" s="1" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="E229" s="2">
         <v>44531.0</v>
@@ -10680,16 +10680,16 @@
     </row>
     <row r="230">
       <c r="A230" s="1" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="B230" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C230" s="1" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="D230" s="1" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E230" s="5">
         <v>45643.0</v>
@@ -10714,16 +10714,16 @@
     </row>
     <row r="231">
       <c r="A231" s="1" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B231" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C231" s="1" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="D231" s="1" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="E231" s="5">
         <v>43448.0</v>
@@ -10748,7 +10748,7 @@
     </row>
     <row r="232">
       <c r="A232" s="1" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="B232" s="1" t="s">
         <v>11</v>
@@ -10757,7 +10757,7 @@
         <v>67</v>
       </c>
       <c r="D232" s="1" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="E232" s="2">
         <v>44274.0</v>
@@ -10766,10 +10766,10 @@
         <v>0</v>
       </c>
       <c r="G232" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H232" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I232" s="4">
         <v>2.0</v>
@@ -10782,16 +10782,16 @@
     </row>
     <row r="233">
       <c r="A233" s="1" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="B233" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C233" s="1" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="D233" s="1" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="E233" s="2">
         <v>44539.0</v>
@@ -10800,10 +10800,10 @@
         <v>0</v>
       </c>
       <c r="G233" s="1" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="H233" s="1" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="I233" s="4">
         <v>2.0</v>
@@ -10816,7 +10816,7 @@
     </row>
     <row r="234">
       <c r="A234" s="1" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="B234" s="1" t="s">
         <v>11</v>
@@ -10825,7 +10825,7 @@
         <v>12</v>
       </c>
       <c r="D234" s="1" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="E234" s="2">
         <v>45356.0</v>
@@ -10834,10 +10834,10 @@
         <v>0</v>
       </c>
       <c r="G234" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H234" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I234" s="4">
         <v>2.0</v>
@@ -10850,7 +10850,7 @@
     </row>
     <row r="235">
       <c r="A235" s="1" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="B235" s="1" t="s">
         <v>11</v>
@@ -10859,7 +10859,7 @@
         <v>57</v>
       </c>
       <c r="D235" s="1" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="E235" s="2">
         <v>45383.0</v>
@@ -10884,16 +10884,16 @@
     </row>
     <row r="236">
       <c r="A236" s="1" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B236" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C236" s="1" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="D236" s="1" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="E236" s="2">
         <v>45999.0</v>
@@ -10902,10 +10902,10 @@
         <v>0</v>
       </c>
       <c r="G236" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H236" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="I236" s="4">
         <v>2.0</v>
@@ -10918,7 +10918,7 @@
     </row>
     <row r="237">
       <c r="A237" s="1" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="B237" s="1" t="s">
         <v>11</v>
@@ -10927,7 +10927,7 @@
         <v>59</v>
       </c>
       <c r="D237" s="1" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="E237" s="2">
         <v>44823.0</v>
@@ -10952,7 +10952,7 @@
     </row>
     <row r="238">
       <c r="A238" s="1" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="B238" s="1" t="s">
         <v>11</v>
@@ -10961,7 +10961,7 @@
         <v>59</v>
       </c>
       <c r="D238" s="1" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="E238" s="2">
         <v>45345.0</v>
@@ -10986,7 +10986,7 @@
     </row>
     <row r="239">
       <c r="A239" s="1" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="B239" s="1" t="s">
         <v>11</v>
@@ -11004,10 +11004,10 @@
         <v>0</v>
       </c>
       <c r="G239" s="1" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H239" s="1" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="I239" s="4">
         <v>2.0</v>
@@ -11020,7 +11020,7 @@
     </row>
     <row r="240">
       <c r="A240" s="1" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="B240" s="1" t="s">
         <v>11</v>
@@ -11029,7 +11029,7 @@
         <v>20</v>
       </c>
       <c r="D240" s="1" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="E240" s="2">
         <v>44592.0</v>
@@ -11038,10 +11038,10 @@
         <v>0</v>
       </c>
       <c r="G240" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H240" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I240" s="4">
         <v>1.0</v>
@@ -11054,7 +11054,7 @@
     </row>
     <row r="241">
       <c r="A241" s="1" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B241" s="1" t="s">
         <v>11</v>
@@ -11063,7 +11063,7 @@
         <v>20</v>
       </c>
       <c r="D241" s="1" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="E241" s="2">
         <v>44958.0</v>
@@ -11072,10 +11072,10 @@
         <v>0</v>
       </c>
       <c r="G241" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H241" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I241" s="4">
         <v>1.0</v>
@@ -11088,7 +11088,7 @@
     </row>
     <row r="242">
       <c r="A242" s="1" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="B242" s="1" t="s">
         <v>11</v>
@@ -11097,7 +11097,7 @@
         <v>20</v>
       </c>
       <c r="D242" s="1" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="E242" s="2">
         <v>44000.0</v>
@@ -11122,7 +11122,7 @@
     </row>
     <row r="243">
       <c r="A243" s="1" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="B243" s="1" t="s">
         <v>11</v>
@@ -11131,7 +11131,7 @@
         <v>20</v>
       </c>
       <c r="D243" s="1" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="E243" s="2">
         <v>45139.0</v>
@@ -11140,10 +11140,10 @@
         <v>0</v>
       </c>
       <c r="G243" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H243" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I243" s="4">
         <v>1.0</v>
@@ -11156,7 +11156,7 @@
     </row>
     <row r="244">
       <c r="A244" s="1" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="B244" s="1" t="s">
         <v>11</v>
@@ -11165,7 +11165,7 @@
         <v>20</v>
       </c>
       <c r="D244" s="1" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="E244" s="2">
         <v>44091.0</v>
@@ -11174,10 +11174,10 @@
         <v>0</v>
       </c>
       <c r="G244" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H244" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I244" s="4">
         <v>1.0</v>
@@ -11190,7 +11190,7 @@
     </row>
     <row r="245">
       <c r="A245" s="1" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B245" s="1" t="s">
         <v>11</v>
@@ -11199,7 +11199,7 @@
         <v>20</v>
       </c>
       <c r="D245" s="1" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="E245" s="5">
         <v>45282.0</v>
@@ -11224,16 +11224,16 @@
     </row>
     <row r="246">
       <c r="A246" s="1" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="B246" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C246" s="1" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="D246" s="1" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="E246" s="2">
         <v>45261.0</v>
@@ -11258,16 +11258,16 @@
     </row>
     <row r="247">
       <c r="A247" s="1" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="B247" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C247" s="1" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="D247" s="1" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="E247" s="2">
         <v>44806.0</v>
@@ -11276,10 +11276,10 @@
         <v>0</v>
       </c>
       <c r="G247" s="1" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H247" s="1" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="I247" s="4">
         <v>1.0</v>
@@ -11292,16 +11292,16 @@
     </row>
     <row r="248">
       <c r="A248" s="1" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="B248" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C248" s="1" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="D248" s="1" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="E248" s="5">
         <v>44547.0</v>
@@ -11310,10 +11310,10 @@
         <v>0</v>
       </c>
       <c r="G248" s="1" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H248" s="1" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="I248" s="4">
         <v>1.0</v>
@@ -11326,16 +11326,16 @@
     </row>
     <row r="249">
       <c r="A249" s="1" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="B249" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C249" s="1" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="D249" s="1" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="E249" s="2">
         <v>45030.0</v>
@@ -11344,10 +11344,10 @@
         <v>0</v>
       </c>
       <c r="G249" s="1" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H249" s="1" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="I249" s="4">
         <v>1.0</v>
@@ -11360,16 +11360,16 @@
     </row>
     <row r="250">
       <c r="A250" s="1" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="B250" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C250" s="1" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="D250" s="1" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="E250" s="2">
         <v>45840.0</v>
@@ -11378,10 +11378,10 @@
         <v>0</v>
       </c>
       <c r="G250" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H250" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I250" s="4">
         <v>1.0</v>
@@ -11394,16 +11394,16 @@
     </row>
     <row r="251">
       <c r="A251" s="1" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="B251" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C251" s="1" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="D251" s="1" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="E251" s="2">
         <v>45810.0</v>
@@ -11412,10 +11412,10 @@
         <v>0</v>
       </c>
       <c r="G251" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H251" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I251" s="4">
         <v>1.0</v>
@@ -11428,7 +11428,7 @@
     </row>
     <row r="252">
       <c r="A252" s="1" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="B252" s="1" t="s">
         <v>11</v>
@@ -11437,7 +11437,7 @@
         <v>64</v>
       </c>
       <c r="D252" s="1" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="E252" s="2">
         <v>46065.0</v>
@@ -11462,7 +11462,7 @@
     </row>
     <row r="253">
       <c r="A253" s="1" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="B253" s="1" t="s">
         <v>11</v>
@@ -11471,7 +11471,7 @@
         <v>64</v>
       </c>
       <c r="D253" s="1" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="E253" s="5">
         <v>45946.0</v>
@@ -11496,7 +11496,7 @@
     </row>
     <row r="254">
       <c r="A254" s="1" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="B254" s="1" t="s">
         <v>11</v>
@@ -11505,7 +11505,7 @@
         <v>64</v>
       </c>
       <c r="D254" s="1" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="E254" s="2">
         <v>46062.0</v>
@@ -11514,10 +11514,10 @@
         <v>1</v>
       </c>
       <c r="G254" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H254" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I254" s="4">
         <v>1.0</v>
@@ -11530,7 +11530,7 @@
     </row>
     <row r="255">
       <c r="A255" s="1" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="B255" s="1" t="s">
         <v>11</v>
@@ -11539,7 +11539,7 @@
         <v>64</v>
       </c>
       <c r="D255" s="1" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="E255" s="2">
         <v>46031.0</v>
@@ -11564,7 +11564,7 @@
     </row>
     <row r="256">
       <c r="A256" s="1" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="B256" s="1" t="s">
         <v>11</v>
@@ -11573,7 +11573,7 @@
         <v>64</v>
       </c>
       <c r="D256" s="1" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="E256" s="2">
         <v>45912.0</v>
@@ -11598,7 +11598,7 @@
     </row>
     <row r="257">
       <c r="A257" s="1" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="B257" s="1" t="s">
         <v>11</v>
@@ -11607,7 +11607,7 @@
         <v>64</v>
       </c>
       <c r="D257" s="1" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="E257" s="2">
         <v>45926.0</v>
@@ -11632,7 +11632,7 @@
     </row>
     <row r="258">
       <c r="A258" s="1" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="B258" s="1" t="s">
         <v>11</v>
@@ -11641,7 +11641,7 @@
         <v>64</v>
       </c>
       <c r="D258" s="1" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="E258" s="5">
         <v>45943.0</v>
@@ -11666,16 +11666,16 @@
     </row>
     <row r="259">
       <c r="A259" s="1" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="B259" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C259" s="1" t="s">
-        <v>13</v>
+        <v>79</v>
       </c>
       <c r="D259" s="1" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="E259" s="2">
         <v>44272.0</v>
@@ -11700,16 +11700,16 @@
     </row>
     <row r="260">
       <c r="A260" s="1" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="B260" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C260" s="1" t="s">
-        <v>13</v>
+        <v>79</v>
       </c>
       <c r="D260" s="1" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="E260" s="5">
         <v>44524.0</v>
@@ -11718,10 +11718,10 @@
         <v>0</v>
       </c>
       <c r="G260" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H260" s="1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="I260" s="4">
         <v>1.0</v>
@@ -11734,16 +11734,16 @@
     </row>
     <row r="261">
       <c r="A261" s="1" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="B261" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C261" s="1" t="s">
-        <v>13</v>
+        <v>79</v>
       </c>
       <c r="D261" s="1" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="E261" s="2">
         <v>44208.0</v>
@@ -11768,16 +11768,16 @@
     </row>
     <row r="262">
       <c r="A262" s="1" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="B262" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C262" s="1" t="s">
-        <v>13</v>
+        <v>79</v>
       </c>
       <c r="D262" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="E262" s="5">
         <v>44496.0</v>
@@ -11786,10 +11786,10 @@
         <v>0</v>
       </c>
       <c r="G262" s="1" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H262" s="1" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="I262" s="4">
         <v>1.0</v>
@@ -11802,16 +11802,16 @@
     </row>
     <row r="263">
       <c r="A263" s="1" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="B263" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C263" s="1" t="s">
-        <v>13</v>
+        <v>79</v>
       </c>
       <c r="D263" s="1" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="E263" s="2">
         <v>44112.0</v>
@@ -11820,10 +11820,10 @@
         <v>0</v>
       </c>
       <c r="G263" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H263" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I263" s="4">
         <v>1.0</v>
@@ -11836,7 +11836,7 @@
     </row>
     <row r="264">
       <c r="A264" s="1" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="B264" s="1" t="s">
         <v>11</v>
@@ -11845,7 +11845,7 @@
         <v>20</v>
       </c>
       <c r="D264" s="1" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="E264" s="2">
         <v>45121.0</v>
@@ -11870,7 +11870,7 @@
     </row>
     <row r="265">
       <c r="A265" s="1" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="B265" s="1" t="s">
         <v>11</v>
@@ -11879,7 +11879,7 @@
         <v>48</v>
       </c>
       <c r="D265" s="1" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="E265" s="2">
         <v>45559.0</v>
@@ -11904,7 +11904,7 @@
     </row>
     <row r="266">
       <c r="A266" s="1" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="B266" s="1" t="s">
         <v>11</v>
@@ -11913,7 +11913,7 @@
         <v>48</v>
       </c>
       <c r="D266" s="1" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="E266" s="2">
         <v>46093.0</v>
@@ -11938,7 +11938,7 @@
     </row>
     <row r="267">
       <c r="A267" s="1" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="B267" s="1" t="s">
         <v>11</v>
@@ -11947,7 +11947,7 @@
         <v>48</v>
       </c>
       <c r="D267" s="1" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="E267" s="2">
         <v>46079.0</v>
@@ -11972,7 +11972,7 @@
     </row>
     <row r="268">
       <c r="A268" s="1" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="B268" s="1" t="s">
         <v>11</v>
@@ -11981,7 +11981,7 @@
         <v>48</v>
       </c>
       <c r="D268" s="1" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E268" s="2">
         <v>45559.0</v>
@@ -12006,7 +12006,7 @@
     </row>
     <row r="269">
       <c r="A269" s="1" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="B269" s="1" t="s">
         <v>11</v>
@@ -12015,7 +12015,7 @@
         <v>48</v>
       </c>
       <c r="D269" s="1" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="E269" s="2">
         <v>45365.0</v>
@@ -12040,7 +12040,7 @@
     </row>
     <row r="270">
       <c r="A270" s="1" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="B270" s="1" t="s">
         <v>11</v>
@@ -12049,7 +12049,7 @@
         <v>48</v>
       </c>
       <c r="D270" s="1" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="E270" s="2">
         <v>44768.0</v>
@@ -12074,7 +12074,7 @@
     </row>
     <row r="271">
       <c r="A271" s="1" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="B271" s="1" t="s">
         <v>11</v>
@@ -12083,7 +12083,7 @@
         <v>48</v>
       </c>
       <c r="D271" s="1" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="E271" s="2">
         <v>45365.0</v>
@@ -12108,16 +12108,16 @@
     </row>
     <row r="272">
       <c r="A272" s="1" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="B272" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C272" s="1" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="D272" s="1" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="E272" s="2">
         <v>45917.0</v>
@@ -12126,10 +12126,10 @@
         <v>0</v>
       </c>
       <c r="G272" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H272" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I272" s="4">
         <v>1.0</v>
@@ -12142,13 +12142,13 @@
     </row>
     <row r="273">
       <c r="A273" s="1" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="B273" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C273" s="1" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="D273" s="1" t="s">
         <v>59</v>
@@ -12160,10 +12160,10 @@
         <v>1</v>
       </c>
       <c r="G273" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H273" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I273" s="4">
         <v>1.0</v>
@@ -12176,16 +12176,16 @@
     </row>
     <row r="274">
       <c r="A274" s="1" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="B274" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C274" s="1" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="D274" s="1" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="E274" s="2">
         <v>45993.0</v>
@@ -12210,16 +12210,16 @@
     </row>
     <row r="275">
       <c r="A275" s="1" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="B275" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C275" s="1" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="D275" s="1" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="E275" s="2">
         <v>45993.0</v>
@@ -12244,16 +12244,16 @@
     </row>
     <row r="276">
       <c r="A276" s="1" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="B276" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C276" s="1" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="D276" s="1" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="E276" s="2">
         <v>44979.0</v>
@@ -12278,16 +12278,16 @@
     </row>
     <row r="277">
       <c r="A277" s="1" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="B277" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C277" s="1" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D277" s="1" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="E277" s="2">
         <v>45765.0</v>
@@ -12312,16 +12312,16 @@
     </row>
     <row r="278">
       <c r="A278" s="1" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="B278" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C278" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D278" s="1" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="E278" s="2">
         <v>44763.0</v>
@@ -12346,16 +12346,16 @@
     </row>
     <row r="279">
       <c r="A279" s="1" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="B279" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C279" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D279" s="1" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="E279" s="2">
         <v>44957.0</v>
@@ -12380,16 +12380,16 @@
     </row>
     <row r="280">
       <c r="A280" s="1" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="B280" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C280" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D280" s="1" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="E280" s="2">
         <v>44868.0</v>
@@ -12398,10 +12398,10 @@
         <v>0</v>
       </c>
       <c r="G280" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H280" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I280" s="4">
         <v>1.0</v>
@@ -12414,16 +12414,16 @@
     </row>
     <row r="281">
       <c r="A281" s="1" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="B281" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C281" s="1" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="D281" s="1" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="E281" s="2">
         <v>46035.0</v>
@@ -12432,10 +12432,10 @@
         <v>1</v>
       </c>
       <c r="G281" s="1" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H281" s="1" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="I281" s="4">
         <v>1.0</v>
@@ -12448,7 +12448,7 @@
     </row>
     <row r="282">
       <c r="A282" s="1" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="B282" s="1" t="s">
         <v>11</v>
@@ -12457,7 +12457,7 @@
         <v>20</v>
       </c>
       <c r="D282" s="1" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="E282" s="2">
         <v>44681.0</v>
@@ -12466,10 +12466,10 @@
         <v>0</v>
       </c>
       <c r="G282" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H282" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I282" s="4">
         <v>1.0</v>
@@ -12482,16 +12482,16 @@
     </row>
     <row r="283">
       <c r="A283" s="1" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="B283" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C283" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D283" s="1" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="E283" s="2">
         <v>44953.0</v>
@@ -12516,16 +12516,16 @@
     </row>
     <row r="284">
       <c r="A284" s="1" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="B284" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C284" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D284" s="1" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="E284" s="2">
         <v>45870.0</v>
@@ -12550,16 +12550,16 @@
     </row>
     <row r="285">
       <c r="A285" s="1" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="B285" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C285" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D285" s="1" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="E285" s="5">
         <v>45637.0</v>
@@ -12584,16 +12584,16 @@
     </row>
     <row r="286">
       <c r="A286" s="1" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="B286" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C286" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D286" s="1" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="E286" s="2">
         <v>46029.0</v>
@@ -12618,16 +12618,16 @@
     </row>
     <row r="287">
       <c r="A287" s="1" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="B287" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C287" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D287" s="1" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="E287" s="2">
         <v>45532.0</v>
@@ -12652,16 +12652,16 @@
     </row>
     <row r="288">
       <c r="A288" s="1" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="B288" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C288" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D288" s="1" t="s">
-        <v>711</v>
+        <v>13</v>
       </c>
       <c r="E288" s="2">
         <v>46029.0</v>
@@ -12670,10 +12670,10 @@
         <v>1</v>
       </c>
       <c r="G288" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H288" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I288" s="4">
         <v>1.0</v>
@@ -12692,7 +12692,7 @@
         <v>11</v>
       </c>
       <c r="C289" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D289" s="1" t="s">
         <v>713</v>
@@ -12726,7 +12726,7 @@
         <v>11</v>
       </c>
       <c r="C290" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D290" s="1" t="s">
         <v>715</v>
@@ -12760,7 +12760,7 @@
         <v>11</v>
       </c>
       <c r="C291" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D291" s="1" t="s">
         <v>717</v>
@@ -12794,10 +12794,10 @@
         <v>11</v>
       </c>
       <c r="C292" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D292" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E292" s="2">
         <v>45894.0</v>
@@ -12828,7 +12828,7 @@
         <v>11</v>
       </c>
       <c r="C293" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D293" s="1" t="s">
         <v>720</v>
@@ -12862,7 +12862,7 @@
         <v>11</v>
       </c>
       <c r="C294" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D294" s="1" t="s">
         <v>722</v>
@@ -12896,7 +12896,7 @@
         <v>11</v>
       </c>
       <c r="C295" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D295" s="1" t="s">
         <v>724</v>
@@ -12930,7 +12930,7 @@
         <v>11</v>
       </c>
       <c r="C296" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D296" s="1" t="s">
         <v>726</v>
@@ -12964,7 +12964,7 @@
         <v>11</v>
       </c>
       <c r="C297" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D297" s="1" t="s">
         <v>728</v>
@@ -12998,7 +12998,7 @@
         <v>11</v>
       </c>
       <c r="C298" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D298" s="1" t="s">
         <v>730</v>
@@ -13032,7 +13032,7 @@
         <v>11</v>
       </c>
       <c r="C299" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D299" s="1" t="s">
         <v>732</v>
@@ -13066,7 +13066,7 @@
         <v>11</v>
       </c>
       <c r="C300" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D300" s="1" t="s">
         <v>734</v>
@@ -13078,10 +13078,10 @@
         <v>0</v>
       </c>
       <c r="G300" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H300" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="I300" s="4">
         <v>1.0</v>
@@ -13168,7 +13168,7 @@
         <v>11</v>
       </c>
       <c r="C303" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D303" s="1" t="s">
         <v>740</v>
@@ -13202,7 +13202,7 @@
         <v>11</v>
       </c>
       <c r="C304" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D304" s="1" t="s">
         <v>742</v>
@@ -13236,7 +13236,7 @@
         <v>11</v>
       </c>
       <c r="C305" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D305" s="1" t="s">
         <v>744</v>
@@ -13270,10 +13270,10 @@
         <v>11</v>
       </c>
       <c r="C306" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D306" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E306" s="2">
         <v>44784.0</v>
@@ -13304,7 +13304,7 @@
         <v>11</v>
       </c>
       <c r="C307" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D307" s="1" t="s">
         <v>747</v>
@@ -13338,7 +13338,7 @@
         <v>11</v>
       </c>
       <c r="C308" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D308" s="1" t="s">
         <v>749</v>
@@ -13350,10 +13350,10 @@
         <v>0</v>
       </c>
       <c r="G308" s="1" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="H308" s="1" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="I308" s="4">
         <v>1.0</v>
@@ -13372,7 +13372,7 @@
         <v>11</v>
       </c>
       <c r="C309" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D309" s="1" t="s">
         <v>751</v>
@@ -13440,7 +13440,7 @@
         <v>11</v>
       </c>
       <c r="C311" s="1" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D311" s="1" t="s">
         <v>756</v>
@@ -13452,10 +13452,10 @@
         <v>0</v>
       </c>
       <c r="G311" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H311" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="I311" s="4">
         <v>1.0</v>
@@ -13486,10 +13486,10 @@
         <v>0</v>
       </c>
       <c r="G312" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H312" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I312" s="4">
         <v>1.0</v>
@@ -13610,7 +13610,7 @@
         <v>11</v>
       </c>
       <c r="C316" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D316" s="1" t="s">
         <v>767</v>
@@ -13622,10 +13622,10 @@
         <v>0</v>
       </c>
       <c r="G316" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H316" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I316" s="4">
         <v>1.0</v>
@@ -13644,7 +13644,7 @@
         <v>11</v>
       </c>
       <c r="C317" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D317" s="1" t="s">
         <v>769</v>
@@ -13656,10 +13656,10 @@
         <v>0</v>
       </c>
       <c r="G317" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H317" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I317" s="4">
         <v>1.0</v>
@@ -13678,7 +13678,7 @@
         <v>11</v>
       </c>
       <c r="C318" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D318" s="1" t="s">
         <v>771</v>
@@ -13690,10 +13690,10 @@
         <v>0</v>
       </c>
       <c r="G318" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H318" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I318" s="4">
         <v>1.0</v>
@@ -13712,7 +13712,7 @@
         <v>11</v>
       </c>
       <c r="C319" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D319" s="1" t="s">
         <v>773</v>
@@ -13724,10 +13724,10 @@
         <v>0</v>
       </c>
       <c r="G319" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H319" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I319" s="4">
         <v>1.0</v>
@@ -13746,7 +13746,7 @@
         <v>11</v>
       </c>
       <c r="C320" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D320" s="1" t="s">
         <v>775</v>
@@ -13758,10 +13758,10 @@
         <v>0</v>
       </c>
       <c r="G320" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H320" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I320" s="4">
         <v>1.0</v>
@@ -13780,7 +13780,7 @@
         <v>11</v>
       </c>
       <c r="C321" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D321" s="1" t="s">
         <v>777</v>
@@ -13792,10 +13792,10 @@
         <v>0</v>
       </c>
       <c r="G321" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H321" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I321" s="4">
         <v>1.0</v>
@@ -13848,10 +13848,10 @@
         <v>11</v>
       </c>
       <c r="C323" s="1" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D323" s="1" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="E323" s="2">
         <v>44958.0</v>
@@ -13882,7 +13882,7 @@
         <v>11</v>
       </c>
       <c r="C324" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D324" s="1" t="s">
         <v>783</v>
@@ -13916,7 +13916,7 @@
         <v>11</v>
       </c>
       <c r="C325" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D325" s="1" t="s">
         <v>785</v>
@@ -13950,7 +13950,7 @@
         <v>11</v>
       </c>
       <c r="C326" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D326" s="1" t="s">
         <v>717</v>
@@ -13984,7 +13984,7 @@
         <v>11</v>
       </c>
       <c r="C327" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D327" s="1" t="s">
         <v>788</v>
@@ -14018,7 +14018,7 @@
         <v>11</v>
       </c>
       <c r="C328" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D328" s="1" t="s">
         <v>790</v>
@@ -14030,10 +14030,10 @@
         <v>0</v>
       </c>
       <c r="G328" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H328" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="I328" s="4">
         <v>1.0</v>
@@ -14052,7 +14052,7 @@
         <v>11</v>
       </c>
       <c r="C329" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D329" s="1" t="s">
         <v>792</v>
@@ -14098,10 +14098,10 @@
         <v>0</v>
       </c>
       <c r="G330" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H330" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I330" s="4">
         <v>1.0</v>
@@ -14120,7 +14120,7 @@
         <v>11</v>
       </c>
       <c r="C331" s="1" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="D331" s="1" t="s">
         <v>797</v>
@@ -14166,10 +14166,10 @@
         <v>0</v>
       </c>
       <c r="G332" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H332" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I332" s="4">
         <v>1.0</v>
@@ -14188,7 +14188,7 @@
         <v>11</v>
       </c>
       <c r="C333" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D333" s="1" t="s">
         <v>802</v>
@@ -14200,10 +14200,10 @@
         <v>0</v>
       </c>
       <c r="G333" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H333" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I333" s="4">
         <v>1.0</v>
@@ -14256,7 +14256,7 @@
         <v>11</v>
       </c>
       <c r="C335" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D335" s="1" t="s">
         <v>807</v>
@@ -14268,10 +14268,10 @@
         <v>0</v>
       </c>
       <c r="G335" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H335" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I335" s="4">
         <v>1.0</v>
@@ -14290,7 +14290,7 @@
         <v>11</v>
       </c>
       <c r="C336" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D336" s="1" t="s">
         <v>809</v>
@@ -14302,10 +14302,10 @@
         <v>0</v>
       </c>
       <c r="G336" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H336" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I336" s="4">
         <v>1.0</v>
@@ -14324,7 +14324,7 @@
         <v>11</v>
       </c>
       <c r="C337" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D337" s="1" t="s">
         <v>811</v>
@@ -14336,10 +14336,10 @@
         <v>0</v>
       </c>
       <c r="G337" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H337" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I337" s="4">
         <v>1.0</v>
@@ -14358,7 +14358,7 @@
         <v>11</v>
       </c>
       <c r="C338" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D338" s="1" t="s">
         <v>813</v>
@@ -14370,10 +14370,10 @@
         <v>0</v>
       </c>
       <c r="G338" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H338" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I338" s="4">
         <v>1.0</v>
@@ -14392,7 +14392,7 @@
         <v>11</v>
       </c>
       <c r="C339" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D339" s="1" t="s">
         <v>815</v>
@@ -14404,10 +14404,10 @@
         <v>0</v>
       </c>
       <c r="G339" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H339" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I339" s="4">
         <v>1.0</v>
@@ -14426,7 +14426,7 @@
         <v>11</v>
       </c>
       <c r="C340" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D340" s="1" t="s">
         <v>817</v>
@@ -14438,10 +14438,10 @@
         <v>0</v>
       </c>
       <c r="G340" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H340" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I340" s="4">
         <v>1.0</v>
@@ -14460,7 +14460,7 @@
         <v>11</v>
       </c>
       <c r="C341" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D341" s="1" t="s">
         <v>819</v>
@@ -14472,10 +14472,10 @@
         <v>0</v>
       </c>
       <c r="G341" s="1" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H341" s="1" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="I341" s="4">
         <v>1.0</v>
@@ -14494,7 +14494,7 @@
         <v>11</v>
       </c>
       <c r="C342" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D342" s="1" t="s">
         <v>821</v>
@@ -14506,10 +14506,10 @@
         <v>0</v>
       </c>
       <c r="G342" s="1" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H342" s="1" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="I342" s="4">
         <v>1.0</v>
@@ -14528,7 +14528,7 @@
         <v>11</v>
       </c>
       <c r="C343" s="1" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="D343" s="1" t="s">
         <v>823</v>
@@ -14574,10 +14574,10 @@
         <v>0</v>
       </c>
       <c r="G344" s="1" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="H344" s="1" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="I344" s="4">
         <v>1.0</v>
@@ -14608,10 +14608,10 @@
         <v>0</v>
       </c>
       <c r="G345" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H345" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I345" s="4">
         <v>1.0</v>
@@ -14676,10 +14676,10 @@
         <v>0</v>
       </c>
       <c r="G347" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H347" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I347" s="4">
         <v>1.0</v>
@@ -14710,10 +14710,10 @@
         <v>0</v>
       </c>
       <c r="G348" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H348" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I348" s="4">
         <v>1.0</v>
@@ -14744,10 +14744,10 @@
         <v>0</v>
       </c>
       <c r="G349" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H349" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I349" s="4">
         <v>1.0</v>
@@ -14812,10 +14812,10 @@
         <v>0</v>
       </c>
       <c r="G351" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H351" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I351" s="4">
         <v>1.0</v>
@@ -14948,10 +14948,10 @@
         <v>0</v>
       </c>
       <c r="G355" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H355" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I355" s="4">
         <v>1.0</v>
@@ -14982,10 +14982,10 @@
         <v>0</v>
       </c>
       <c r="G356" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H356" s="1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="I356" s="4">
         <v>1.0</v>
@@ -15038,7 +15038,7 @@
         <v>11</v>
       </c>
       <c r="C358" s="1" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="D358" s="1" t="s">
         <v>856</v>
@@ -15050,10 +15050,10 @@
         <v>0</v>
       </c>
       <c r="G358" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H358" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="I358" s="4">
         <v>1.0</v>
@@ -15109,7 +15109,7 @@
         <v>59</v>
       </c>
       <c r="D360" s="1" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="E360" s="2">
         <v>42916.0</v>

--- a/Car_Wash_Advisory_Top_Acquisitions.xlsx
+++ b/Car_Wash_Advisory_Top_Acquisitions.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2593" uniqueCount="886">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2607" uniqueCount="890">
   <si>
     <t>Title -- Who Bought What?</t>
   </si>
@@ -2669,6 +2669,18 @@
   </si>
   <si>
     <t>Aqua Super Express Car Wash</t>
+  </si>
+  <si>
+    <t>Club Car Wash Acquires Alton Auto Butler Property</t>
+  </si>
+  <si>
+    <t>Alton Auto Butler</t>
+  </si>
+  <si>
+    <t>Splash Car Wash Acquires Green Ocean Car Wash</t>
+  </si>
+  <si>
+    <t>Green Ocean Car Wash</t>
   </si>
 </sst>
 </file>
@@ -15530,30 +15542,70 @@
       <c r="L370" s="1"/>
     </row>
     <row r="371">
-      <c r="A371" s="1"/>
-      <c r="B371" s="1"/>
-      <c r="C371" s="1"/>
-      <c r="D371" s="1"/>
-      <c r="E371" s="1"/>
-      <c r="F371" s="1"/>
-      <c r="G371" s="1"/>
-      <c r="H371" s="1"/>
-      <c r="I371" s="1"/>
-      <c r="J371" s="1"/>
+      <c r="A371" s="1" t="s">
+        <v>886</v>
+      </c>
+      <c r="B371" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C371" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D371" s="1" t="s">
+        <v>887</v>
+      </c>
+      <c r="E371" s="2">
+        <v>46193.0</v>
+      </c>
+      <c r="F371" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G371" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="H371" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="I371" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="J371" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="K371" s="1"/>
       <c r="L371" s="1"/>
     </row>
     <row r="372">
-      <c r="A372" s="1"/>
-      <c r="B372" s="1"/>
-      <c r="C372" s="1"/>
-      <c r="D372" s="1"/>
-      <c r="E372" s="1"/>
-      <c r="F372" s="1"/>
-      <c r="G372" s="1"/>
-      <c r="H372" s="1"/>
-      <c r="I372" s="1"/>
-      <c r="J372" s="1"/>
+      <c r="A372" s="1" t="s">
+        <v>888</v>
+      </c>
+      <c r="B372" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C372" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="D372" s="1" t="s">
+        <v>889</v>
+      </c>
+      <c r="E372" s="2">
+        <v>46220.0</v>
+      </c>
+      <c r="F372" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G372" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="H372" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="I372" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="J372" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="K372" s="1"/>
       <c r="L372" s="1"/>
     </row>
